--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1111,23 +1111,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="I3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.15</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I3" t="n">
         <v>2.88</v>
@@ -1144,7 +1144,7 @@
         <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -1102,239 +1102,493 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>3.4</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>3.9</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>2.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>2.88</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>2.8</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>3.15</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-07 11:15:26</t>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,189 +1097,189 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>12</v>
       </c>
-      <c r="Y3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
         <v>1.01</v>
@@ -1291,13 +1291,13 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.01</v>
@@ -1309,286 +1309,1556 @@
         <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
         <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
         <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sandvikens IF</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Falkenbergs</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-07 15:32:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oddevold</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Norrkoping</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-07 15:32:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IK Brage</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ljungskile</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-07 15:32:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CD Castellon</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-07 15:32:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-07 15:32:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G9" t="n">
         <v>3.9</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H9" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I9" t="n">
         <v>2.88</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J9" t="n">
         <v>2.8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K9" t="n">
         <v>3.15</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-07 13:23:55</t>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
         <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -872,16 +872,16 @@
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -896,13 +896,13 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
@@ -1150,13 +1150,13 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1467,7 +1467,7 @@
         <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>26</v>
@@ -1512,7 +1512,7 @@
         <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1527,68 +1527,68 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1790,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
@@ -1808,13 +1808,13 @@
         <v>20</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
@@ -1826,23 +1826,23 @@
         <v>19.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>21</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>2.6</v>
@@ -1885,7 +1885,7 @@
         <v>2.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
@@ -1906,16 +1906,16 @@
         <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
         <v>2.44</v>
@@ -1978,7 +1978,7 @@
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
@@ -2038,65 +2038,65 @@
         <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>6.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
         <v>19.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
       </c>
       <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.85</v>
       </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.7</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2393,10 +2393,10 @@
         <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.45</v>
@@ -2405,34 +2405,34 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2441,7 +2441,7 @@
         <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
         <v>95</v>
@@ -2450,7 +2450,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>19</v>
@@ -2468,10 +2468,10 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2486,7 +2486,7 @@
         <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
         <v>9</v>
@@ -2495,16 +2495,16 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
       </c>
       <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
         <v>12.5</v>
@@ -2516,19 +2516,19 @@
         <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
         <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD8" t="n">
         <v>4.8</v>
@@ -2537,10 +2537,10 @@
         <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
         <v>2.92</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -860,7 +860,7 @@
         <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
         <v>2.5</v>
@@ -890,19 +890,19 @@
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
         <v>3.45</v>
@@ -1126,7 +1126,7 @@
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1141,10 +1141,10 @@
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
@@ -1168,7 +1168,7 @@
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
         <v>44</v>
@@ -1186,7 +1186,7 @@
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>22</v>
@@ -1198,7 +1198,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>36</v>
@@ -1213,64 +1213,64 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="AR3" t="n">
         <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>2.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>2.06</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AX3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.8</v>
+        <v>2.12</v>
       </c>
       <c r="AZ3" t="n">
         <v>9.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>2.26</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.5</v>
+        <v>2.32</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
         <v>2.76</v>
@@ -1398,7 +1398,7 @@
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
@@ -1416,7 +1416,7 @@
         <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1449,7 +1449,7 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>44</v>
@@ -1461,7 +1461,7 @@
         <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
         <v>85</v>
@@ -1482,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
@@ -1494,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1506,25 +1506,25 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.95</v>
@@ -1548,13 +1548,13 @@
         <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2.52</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
@@ -1637,7 +1637,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1736,7 +1736,7 @@
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1760,19 +1760,19 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
         <v>19.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
         <v>14</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1906,16 +1906,16 @@
         <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U6" t="n">
         <v>2.44</v>
@@ -2002,7 +2002,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -2014,19 +2014,19 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
         <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
         <v>17</v>
@@ -2056,7 +2056,7 @@
         <v>6.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -2130,169 +2130,169 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="I7" t="n">
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
       </c>
       <c r="L7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.32</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
         <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
         <v>2.42</v>
@@ -2390,7 +2390,7 @@
         <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -2414,7 +2414,7 @@
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
@@ -2429,10 +2429,10 @@
         <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2468,7 +2468,7 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
         <v>34</v>
@@ -2531,10 +2531,10 @@
         <v>4.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
@@ -2552,19 +2552,19 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.46</v>
+        <v>15.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
         <v>18.5</v>
@@ -2582,7 +2582,7 @@
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -2653,16 +2653,16 @@
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
         <v>1.41</v>
@@ -2671,194 +2671,194 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -863,7 +863,7 @@
         <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -884,7 +884,7 @@
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
@@ -902,7 +902,7 @@
         <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1482,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
@@ -1512,13 +1512,13 @@
         <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
         <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1554,7 +1554,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -2056,7 +2056,7 @@
         <v>6.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2130,227 +2130,227 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="V7" t="n">
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.78</v>
+        <v>2.72</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.77</v>
+        <v>9.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.81</v>
+        <v>2.78</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
         <v>2.42</v>
@@ -2426,10 +2426,10 @@
         <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
         <v>1.7</v>
@@ -2564,13 +2564,13 @@
         <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.65</v>
@@ -2677,10 +2677,10 @@
         <v>6.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.53</v>
@@ -2689,7 +2689,7 @@
         <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>9.199999999999999</v>
@@ -2746,119 +2746,119 @@
         <v>2.48</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AR9" t="n">
         <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.68</v>
+        <v>2.06</v>
       </c>
       <c r="AU9" t="n">
         <v>5.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="AX9" t="n">
         <v>15.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.15</v>
+        <v>2.32</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
         <v>2.44</v>
@@ -866,7 +866,7 @@
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>4.3</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
         <v>1.63</v>
@@ -1150,7 +1150,7 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1165,112 +1165,112 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="n">
         <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.44</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.24</v>
+        <v>5.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.44</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.32</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.44</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
         <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1395,7 +1395,7 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
         <v>1.76</v>
@@ -1407,28 +1407,28 @@
         <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
         <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
         <v>15</v>
@@ -1437,7 +1437,7 @@
         <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>34</v>
@@ -1452,7 +1452,7 @@
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
@@ -1470,7 +1470,7 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1482,19 +1482,19 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1506,25 +1506,25 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.95</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>7</v>
@@ -1769,7 +1769,7 @@
         <v>19.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
         <v>7.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
@@ -2002,7 +2002,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -2014,13 +2014,13 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
         <v>25</v>
@@ -2044,31 +2044,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2077,26 +2077,26 @@
         <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>3.3</v>
@@ -2154,31 +2154,31 @@
         <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
         <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2193,7 +2193,7 @@
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
         <v>9.6</v>
@@ -2229,67 +2229,67 @@
         <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO7" t="n">
         <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
         <v>3.35</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BN7" t="n">
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BT7" t="n">
         <v>970</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -2552,7 +2552,7 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2570,7 +2570,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2656,13 +2656,13 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
         <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
         <v>1.41</v>
@@ -2674,7 +2674,7 @@
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.88</v>
@@ -2755,7 +2755,7 @@
         <v>2.38</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="AU9" t="n">
         <v>5.9</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.25</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.22</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -911,176 +911,176 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1114,49 +1114,49 @@
         <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q3" t="n">
         <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1165,112 +1165,112 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
         <v>75</v>
       </c>
       <c r="AB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
         <v>970</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF3" t="n">
         <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>21</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO3" t="n">
         <v>34</v>
       </c>
-      <c r="AK3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>42</v>
-      </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BG3" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1404,16 +1404,16 @@
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>1.58</v>
@@ -1422,25 +1422,25 @@
         <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
         <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1461,7 +1461,7 @@
         <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>85</v>
@@ -1470,7 +1470,7 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1479,16 +1479,16 @@
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1506,19 +1506,19 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD4" t="n">
         <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1527,7 +1527,7 @@
         <v>15.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI4" t="n">
         <v>3.1</v>
@@ -1536,16 +1536,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO4" t="n">
         <v>4.5</v>
@@ -1554,41 +1554,41 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1646,25 +1646,25 @@
         <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T5" t="n">
         <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1673,7 +1673,7 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
         <v>14.5</v>
@@ -1688,7 +1688,7 @@
         <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -1772,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
         <v>14</v>
@@ -1781,22 +1781,22 @@
         <v>13</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
@@ -1805,16 +1805,16 @@
         <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
@@ -1826,23 +1826,23 @@
         <v>19.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>21</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H6" t="n">
         <v>2.6</v>
@@ -1885,7 +1885,7 @@
         <v>2.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
@@ -1897,28 +1897,28 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V6" t="n">
         <v>1.57</v>
@@ -1927,10 +1927,10 @@
         <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1939,10 +1939,10 @@
         <v>38</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>12</v>
@@ -1978,7 +1978,7 @@
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
@@ -2002,7 +2002,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -2014,19 +2014,19 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
         <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
         <v>17</v>
@@ -2035,7 +2035,7 @@
         <v>13</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
         <v>3</v>
@@ -2068,7 +2068,7 @@
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2080,7 +2080,7 @@
         <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
@@ -2089,14 +2089,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
         <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
@@ -2139,64 +2139,64 @@
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.52</v>
       </c>
       <c r="V7" t="n">
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -2208,112 +2208,112 @@
         <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>30</v>
       </c>
       <c r="AM7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BN7" t="n">
         <v>5.5</v>
       </c>
-      <c r="BA7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ7" t="n">
         <v>8.4</v>
@@ -2322,10 +2322,10 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.76</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
         <v>5.8</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.82</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2662,13 +2662,13 @@
         <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
         <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -890,19 +890,19 @@
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
         <v>1.64</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -914,22 +914,22 @@
         <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
         <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>42</v>
@@ -944,7 +944,7 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>32</v>
@@ -956,7 +956,7 @@
         <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
         <v>970</v>
@@ -965,122 +965,122 @@
         <v>34</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="BT2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1138,7 +1138,7 @@
         <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
         <v>2.34</v>
@@ -1150,13 +1150,13 @@
         <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
         <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1177,7 +1177,7 @@
         <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1201,10 +1201,10 @@
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
@@ -1219,122 +1219,122 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
         <v>2.74</v>
@@ -1374,7 +1374,7 @@
         <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1395,13 +1395,13 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
         <v>2.86</v>
@@ -1410,10 +1410,10 @@
         <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
         <v>1.58</v>
@@ -1425,16 +1425,16 @@
         <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
         <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
@@ -1455,22 +1455,22 @@
         <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1479,10 +1479,10 @@
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
@@ -1494,31 +1494,31 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1527,49 +1527,49 @@
         <v>15.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW4" t="n">
         <v>7.2</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
@@ -1652,7 +1652,7 @@
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
@@ -1736,7 +1736,7 @@
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
         <v>7</v>
@@ -1769,7 +1769,7 @@
         <v>19.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
         <v>7.6</v>
@@ -1781,22 +1781,22 @@
         <v>13</v>
       </c>
       <c r="BH5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
@@ -1808,13 +1808,13 @@
         <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
@@ -1826,23 +1826,23 @@
         <v>19.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>21</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
         <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1903,25 +1903,25 @@
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
         <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U6" t="n">
         <v>2.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.51</v>
@@ -1945,10 +1945,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
         <v>23</v>
@@ -1960,7 +1960,7 @@
         <v>15.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
         <v>42</v>
@@ -1972,7 +1972,7 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN6" t="n">
         <v>21</v>
@@ -2002,7 +2002,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -2020,13 +2020,13 @@
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
         <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>17</v>
@@ -2035,7 +2035,7 @@
         <v>13</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
         <v>3</v>
@@ -2050,13 +2050,13 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
@@ -2065,10 +2065,10 @@
         <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2077,26 +2077,26 @@
         <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
         <v>3.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X7" t="n">
         <v>25</v>
@@ -2190,10 +2190,10 @@
         <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
@@ -2211,25 +2211,25 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
         <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
         <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>23</v>
@@ -2238,13 +2238,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
         <v>11.5</v>
@@ -2253,13 +2253,13 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2268,25 +2268,25 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2310,7 +2310,7 @@
         <v>5.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP7" t="n">
         <v>16</v>
@@ -2343,14 +2343,14 @@
         <v>11</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA7" t="n">
         <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
         <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -2408,22 +2408,22 @@
         <v>2.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
         <v>1.91</v>
@@ -2438,13 +2438,13 @@
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
         <v>9.199999999999999</v>
@@ -2453,7 +2453,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
         <v>65</v>
@@ -2480,13 +2480,13 @@
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
         <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
         <v>9</v>
@@ -2495,10 +2495,10 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2510,7 +2510,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2519,28 +2519,28 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH8" t="n">
         <v>2.92</v>
@@ -2552,13 +2552,13 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
@@ -2570,41 +2570,41 @@
         <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>3.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H9" t="n">
         <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J9" t="n">
         <v>2.8</v>
@@ -2653,212 +2653,212 @@
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P9" t="n">
         <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>12</v>
-      </c>
       <c r="AC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW9" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.63</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.64</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -914,22 +914,22 @@
         <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
         <v>970</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>42</v>
@@ -938,25 +938,25 @@
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
         <v>970</v>
@@ -965,122 +965,122 @@
         <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE2" t="n">
         <v>5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.42</v>
+        <v>3.95</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1138,7 +1138,7 @@
         <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
         <v>2.34</v>
@@ -1156,7 +1156,7 @@
         <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1165,118 +1165,118 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK3" t="n">
         <v>24</v>
       </c>
-      <c r="Y3" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>970</v>
-      </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AP3" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AT3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="n">
         <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1365,85 +1365,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="n">
         <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD4" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1452,7 +1452,7 @@
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
         <v>42</v>
@@ -1464,61 +1464,61 @@
         <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
         <v>7.8</v>
       </c>
       <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY4" t="n">
         <v>10</v>
       </c>
-      <c r="AW4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1536,13 +1536,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
         <v>6</v>
@@ -1554,41 +1554,41 @@
         <v>19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
@@ -1637,7 +1637,7 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1655,16 +1655,16 @@
         <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1673,61 +1673,61 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
         <v>15</v>
       </c>
-      <c r="AC5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
@@ -1736,13 +1736,13 @@
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
         <v>9.199999999999999</v>
@@ -1751,34 +1751,34 @@
         <v>19</v>
       </c>
       <c r="AX5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BG5" t="n">
         <v>14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>13</v>
       </c>
       <c r="BH5" t="n">
         <v>3.9</v>
@@ -1802,7 +1802,7 @@
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
         <v>21</v>
@@ -1811,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS5" t="n">
         <v>7.8</v>
@@ -1820,7 +1820,7 @@
         <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>19.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
         <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
@@ -1897,7 +1897,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -1906,7 +1906,7 @@
         <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>1.46</v>
@@ -1918,25 +1918,25 @@
         <v>1.58</v>
       </c>
       <c r="U6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
         <v>15</v>
@@ -1951,7 +1951,7 @@
         <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1981,58 +1981,58 @@
         <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>11</v>
       </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB6" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB6" t="n">
-        <v>32</v>
-      </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BG6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.95</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
         <v>3.8</v>
@@ -2145,73 +2145,73 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.7</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.68</v>
-      </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
         <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
         <v>38</v>
@@ -2220,79 +2220,79 @@
         <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
         <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
         <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
         <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>19</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
@@ -2304,25 +2304,25 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
         <v>16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>6.6</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
         <v>19</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
         <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -2408,13 +2408,13 @@
         <v>2.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
@@ -2423,31 +2423,31 @@
         <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
         <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>8.199999999999999</v>
@@ -2465,13 +2465,13 @@
         <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2480,16 +2480,16 @@
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
         <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
@@ -2504,43 +2504,43 @@
         <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
         <v>5.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
         <v>5.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
         <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE8" t="n">
         <v>5.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="n">
         <v>2.92</v>
@@ -2552,59 +2552,59 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP8" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT8" t="n">
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H9" t="n">
         <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2665,7 +2665,7 @@
         <v>1.66</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q9" t="n">
         <v>3</v>
@@ -2677,28 +2677,28 @@
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
         <v>7.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB9" t="n">
         <v>9.199999999999999</v>
@@ -2710,10 +2710,10 @@
         <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>18</v>
@@ -2725,7 +2725,7 @@
         <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="n">
         <v>70</v>
@@ -2749,13 +2749,13 @@
         <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT9" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
@@ -2764,37 +2764,37 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY9" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8</v>
       </c>
-      <c r="BD9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="n">
         <v>2.56</v>
@@ -2851,14 +2851,14 @@
         <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA9" t="n">
         <v>9.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>2.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP2" t="n">
         <v>29</v>
       </c>
-      <c r="AA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="BQ2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG2" t="n">
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU2" t="n">
         <v>4.6</v>
       </c>
-      <c r="BH2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>950</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.97</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1102,61 +1102,61 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1165,176 +1165,176 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY3" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.2</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO3" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>1.97</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>3.85</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
-        <v>2.76</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS4" t="n">
         <v>4.4</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X4" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AT4" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AU4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC4" t="n">
         <v>14</v>
       </c>
-      <c r="AH4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="BD4" t="n">
         <v>21</v>
       </c>
-      <c r="AO4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BE4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1610,31 +1610,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.88</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.78</v>
-      </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1649,200 +1649,200 @@
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
         <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
         <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z5" t="n">
         <v>24</v>
       </c>
-      <c r="Y5" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>21</v>
-      </c>
       <c r="AA5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
         <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT5" t="n">
         <v>10</v>
       </c>
-      <c r="AR5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12</v>
-      </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>29</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ5" t="n">
         <v>7</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
         <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
         <v>21</v>
       </c>
       <c r="CA5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1897,70 +1897,70 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
         <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
         <v>42</v>
@@ -1972,138 +1972,138 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9</v>
-      </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA6" t="n">
         <v>7.4</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="J7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.8</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK7" t="n">
         <v>29</v>
       </c>
-      <c r="AA7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG7" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>16.5</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,498 +2367,1514 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kawkab Marrakech</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Raja Casablanca</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CD Castellon</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MAS Maghrib A Fes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="F13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.5</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="I13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L13" t="n">
         <v>1.58</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M13" t="n">
         <v>1.16</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N13" t="n">
         <v>2.28</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O13" t="n">
         <v>1.66</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P13" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R13" t="n">
         <v>1.15</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S13" t="n">
         <v>6.4</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="T13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.66</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="V13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y13" t="n">
         <v>7.4</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z13" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA13" t="n">
         <v>46</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE13" t="n">
         <v>46</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF13" t="n">
         <v>25</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG13" t="n">
         <v>18</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH13" t="n">
         <v>29</v>
       </c>
-      <c r="AI9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AI13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
         <v>70</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL13" t="n">
         <v>120</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM13" t="n">
         <v>300</v>
       </c>
-      <c r="AN9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="AN13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ13" t="n">
         <v>6</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS13" t="n">
         <v>36</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT13" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>6</v>
       </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BA13" t="n">
         <v>7</v>
       </c>
-      <c r="AX9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA9" t="n">
+      <c r="BB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BF13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW13" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>9.4</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="BZ13" t="n">
         <v>70</v>
       </c>
-      <c r="CA9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-08 06:27:16</t>
+      <c r="CA13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,60 +843,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Livyi Bereh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.18</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.58</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1019,75 +1019,75 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>2.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK3" t="n">
         <v>42</v>
       </c>
-      <c r="AF3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>27</v>
-      </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH3" t="n">
+      <c r="BO3" t="n">
         <v>3.75</v>
       </c>
-      <c r="BI3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1356,62 +1356,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.65</v>
       </c>
-      <c r="I4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.28</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.48</v>
-      </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
@@ -1419,176 +1419,176 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS4" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
         <v>4.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>1.97</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1610,202 +1610,202 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.54</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y5" t="n">
         <v>23</v>
       </c>
-      <c r="Y5" t="n">
-        <v>16</v>
-      </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
         <v>15.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK5" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP5" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>19</v>
       </c>
       <c r="BQ5" t="n">
         <v>7</v>
@@ -1814,35 +1814,35 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>8</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1864,100 +1864,100 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.59</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X6" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z6" t="n">
         <v>24</v>
       </c>
-      <c r="Y6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>21</v>
-      </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
         <v>42</v>
@@ -1969,134 +1969,134 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
         <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
         <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
         <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -2118,169 +2118,169 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
         <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
         <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
         <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
         <v>15</v>
       </c>
-      <c r="Z7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
         <v>15</v>
       </c>
-      <c r="AC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
         <v>14</v>
@@ -2289,40 +2289,40 @@
         <v>13.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
@@ -2334,30 +2334,30 @@
         <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA7" t="n">
         <v>7.4</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.16</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="Q8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X8" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK8" t="n">
         <v>4.8</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -2626,73 +2626,73 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.87</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2701,22 +2701,22 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2743,16 +2743,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
         <v>1.01</v>
@@ -2764,7 +2764,7 @@
         <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
         <v>1.01</v>
@@ -2773,22 +2773,22 @@
         <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2797,75 +2797,75 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.42</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO10" t="n">
         <v>4.9</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="X10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>21</v>
-      </c>
       <c r="BW10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>2.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.800000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
-        <v>2.46</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BU12" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,747 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="F14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I14" t="n">
         <v>2.6</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>2.84</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L14" t="n">
         <v>1.58</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>1.16</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N14" t="n">
         <v>2.28</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O14" t="n">
         <v>1.66</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P14" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1.15</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>6.4</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>2.26</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="U14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.63</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="W14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="BB14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV14" t="n">
         <v>25</v>
       </c>
-      <c r="AG13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="BW14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>70</v>
       </c>
-      <c r="AL13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI13" t="n">
+      <c r="CA14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>2.12</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>75</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU13" t="n">
+      <c r="G15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BV13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>70</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-08 08:36:03</t>
+      <c r="BI15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,46 +857,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
         <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>1.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,168 +1097,168 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Agrobiznes Volochysk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>FK Kudrivka</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
         <v>1.03</v>
@@ -1273,75 +1273,75 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>1.43</v>
       </c>
       <c r="BP3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>3.4</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="AR4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.2</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE4" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG4" t="n">
         <v>4.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>2.06</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1610,61 +1610,61 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.65</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1673,176 +1673,176 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="BG5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10.5</v>
+        <v>1.97</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.48</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.36</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y6" t="n">
         <v>23</v>
       </c>
-      <c r="Y6" t="n">
-        <v>16</v>
-      </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
         <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
         <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2118,73 +2118,73 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
         <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
         <v>24</v>
@@ -2193,164 +2193,164 @@
         <v>48</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO7" t="n">
         <v>24</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AP7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>27</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>5.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2405,213 +2405,213 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>1.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AF8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="n">
         <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.87</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BA8" t="n">
-        <v>2.6</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.88</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.88</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.88</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.88</v>
+        <v>15.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
         <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
         <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA8" t="n">
         <v>7.4</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,244 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>2.86</v>
       </c>
       <c r="J9" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.24</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>22</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA9" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>2.94</v>
       </c>
       <c r="H10" t="n">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>50</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.15</v>
+        <v>1.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,210 +3129,210 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>4.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO11" t="n">
         <v>4.9</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BP11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3341,39 +3341,39 @@
         <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX11" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="G12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.9</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.42</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU12" t="n">
         <v>8</v>
       </c>
-      <c r="Z12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV12" t="n">
         <v>21</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="G13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.44</v>
       </c>
-      <c r="H13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.96</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AI13" t="n">
         <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM13" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
       </c>
       <c r="BB13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG13" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD13" t="n">
+      <c r="BH13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF13" t="n">
+      <c r="BU13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV13" t="n">
         <v>21</v>
       </c>
-      <c r="BG13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>34</v>
-      </c>
       <c r="BW13" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA13" t="n">
         <v>11</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -3896,493 +3896,747 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>2.96</v>
       </c>
       <c r="O14" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU14" t="n">
         <v>6.4</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AV14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>18</v>
       </c>
-      <c r="AH14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="BA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6</v>
-      </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>75</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BZ14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>70</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-08 12:53:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Atletico Ottawa</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>FC Supra du Quebec</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="F16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H16" t="n">
         <v>3.15</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="I16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L16" t="n">
         <v>1.01</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>1.05</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="N16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.01</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="BG16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="BH16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>1.01</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-06-08 10:44:40</t>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -860,10 +860,10 @@
         <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>2.48</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
         <v>22</v>
@@ -872,7 +872,7 @@
         <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -1111,46 +1111,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="n">
         <v>2.54</v>
@@ -1377,55 +1377,55 @@
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K4" t="n">
         <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
         <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
         <v>10</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
@@ -1437,7 +1437,7 @@
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>75</v>
@@ -1449,13 +1449,13 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
         <v>42</v>
@@ -1464,37 +1464,37 @@
         <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
         <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1506,89 +1506,89 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.6</v>
       </c>
-      <c r="BF4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.16</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.98</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.08</v>
+        <v>8.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -1628,13 +1628,13 @@
         <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1655,7 +1655,7 @@
         <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
         <v>2.78</v>
@@ -1688,7 +1688,7 @@
         <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1730,7 +1730,7 @@
         <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
         <v>4.9</v>
@@ -1745,7 +1745,7 @@
         <v>3.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW5" t="n">
         <v>4.7</v>
@@ -1757,16 +1757,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
         <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
         <v>4.7</v>
@@ -1778,7 +1778,7 @@
         <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1790,59 +1790,59 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>3.95</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5.1</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>7.4</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2160,37 +2160,37 @@
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
         <v>15.5</v>
@@ -2199,13 +2199,13 @@
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
@@ -2217,7 +2217,7 @@
         <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
@@ -2229,10 +2229,10 @@
         <v>75</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
         <v>14.5</v>
@@ -2244,7 +2244,7 @@
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2268,19 +2268,19 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
         <v>19.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF7" t="n">
         <v>13.5</v>
@@ -2298,22 +2298,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
         <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.8</v>
@@ -2325,32 +2325,32 @@
         <v>7.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>22</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>21</v>
       </c>
       <c r="CA7" t="n">
         <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2414,19 +2414,19 @@
         <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
         <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2435,19 +2435,19 @@
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>16.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2462,10 +2462,10 @@
         <v>22</v>
       </c>
       <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
         <v>36</v>
@@ -2477,16 +2477,16 @@
         <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN8" t="n">
         <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>16.5</v>
@@ -2498,13 +2498,13 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
         <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
@@ -2525,16 +2525,16 @@
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
         <v>15.5</v>
@@ -2564,7 +2564,7 @@
         <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
         <v>20</v>
@@ -2582,7 +2582,7 @@
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>20</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>2.62</v>
       </c>
       <c r="I9" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J9" t="n">
         <v>3.55</v>
@@ -2800,7 +2800,7 @@
         <v>4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.199999999999999</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>6.2</v>
@@ -2830,7 +2830,7 @@
         <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT9" t="n">
         <v>6.2</v>
@@ -2839,7 +2839,7 @@
         <v>4.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW9" t="n">
         <v>6.6</v>
@@ -2848,17 +2848,17 @@
         <v>30</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>22</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
         <v>3.3</v>
@@ -2901,7 +2901,7 @@
         <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
@@ -2913,7 +2913,7 @@
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
         <v>1.57</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J11" t="n">
         <v>2.92</v>
@@ -3167,13 +3167,13 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
         <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
         <v>2.8</v>
@@ -3191,7 +3191,7 @@
         <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="W11" t="n">
         <v>1.2</v>
@@ -3308,7 +3308,7 @@
         <v>2.64</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
         <v>3.9</v>
@@ -3421,49 +3421,49 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
         <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9</v>
@@ -3475,7 +3475,7 @@
         <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -3487,22 +3487,22 @@
         <v>36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
         <v>17.5</v>
@@ -3520,7 +3520,7 @@
         <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
@@ -3535,7 +3535,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>30</v>
@@ -3547,22 +3547,22 @@
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
@@ -3574,22 +3574,22 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
         <v>5.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
         <v>10</v>
@@ -3607,20 +3607,20 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
         <v>4.8</v>
@@ -3660,7 +3660,7 @@
         <v>2.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="J13" t="n">
         <v>2.94</v>
@@ -3678,7 +3678,7 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
         <v>1.48</v>
@@ -3690,7 +3690,7 @@
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T13" t="n">
         <v>2.18</v>
@@ -3699,7 +3699,7 @@
         <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="W13" t="n">
         <v>1.16</v>
@@ -3816,7 +3816,7 @@
         <v>2.66</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         <v>1.93</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
         <v>1.69</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
         <v>2.28</v>
       </c>
       <c r="O15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
         <v>1.43</v>
@@ -4360,7 +4360,7 @@
         <v>5.3</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV15" t="n">
         <v>25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4440,19 +4440,19 @@
         <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
@@ -4461,118 +4461,118 @@
         <v>1.86</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU16" t="n">
         <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BE16" t="n">
         <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="n">
         <v>4.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -866,10 +866,10 @@
         <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>10</v>
@@ -896,16 +896,16 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1120,25 +1120,25 @@
         <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.55</v>
@@ -1147,194 +1147,194 @@
         <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.43</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.43</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
         <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1413,7 +1413,7 @@
         <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.64</v>
@@ -1434,7 +1434,7 @@
         <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
@@ -1476,13 +1476,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
         <v>5.5</v>
@@ -1494,7 +1494,7 @@
         <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1506,25 +1506,25 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5</v>
       </c>
-      <c r="BE4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
@@ -1536,7 +1536,7 @@
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
         <v>22</v>
@@ -1566,7 +1566,7 @@
         <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
@@ -1655,13 +1655,13 @@
         <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
         <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
         <v>2.28</v>
@@ -1709,13 +1709,13 @@
         <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
@@ -1730,55 +1730,55 @@
         <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
         <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
         <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1909,7 +1909,7 @@
         <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
         <v>2.56</v>
@@ -1930,7 +1930,7 @@
         <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
         <v>38</v>
@@ -1945,7 +1945,7 @@
         <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE6" t="n">
         <v>48</v>
@@ -1957,7 +1957,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>50</v>
@@ -1978,61 +1978,61 @@
         <v>12.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
         <v>9.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BH6" t="n">
         <v>4.2</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
         <v>5.1</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>7.4</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H7" t="n">
         <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2151,19 +2151,19 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
         <v>2.8</v>
@@ -2172,10 +2172,10 @@
         <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
@@ -2199,7 +2199,7 @@
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
         <v>30</v>
@@ -2226,7 +2226,7 @@
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="n">
         <v>970</v>
@@ -2250,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
@@ -2268,25 +2268,25 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV7" t="n">
         <v>20</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>3.75</v>
@@ -2408,7 +2408,7 @@
         <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
         <v>2.32</v>
@@ -2423,7 +2423,7 @@
         <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.46</v>
@@ -2525,7 +2525,7 @@
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
@@ -2534,7 +2534,7 @@
         <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
         <v>15.5</v>
@@ -2546,7 +2546,7 @@
         <v>3.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
         <v>1.54</v>
@@ -2695,7 +2695,7 @@
         <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
         <v>40</v>
@@ -2734,7 +2734,7 @@
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN9" t="n">
         <v>21</v>
@@ -2752,7 +2752,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2776,10 +2776,10 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
         <v>7</v>
@@ -2788,7 +2788,7 @@
         <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,7 +2913,7 @@
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.57</v>
@@ -2928,28 +2928,28 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2961,10 +2961,10 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2973,16 +2973,16 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2991,64 +2991,64 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.82</v>
+        <v>3.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.52</v>
+        <v>3.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.51</v>
+        <v>5.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.66</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA10" t="n">
         <v>1.64</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BB10" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J11" t="n">
         <v>2.92</v>
@@ -3167,16 +3167,16 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
         <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
@@ -3191,7 +3191,7 @@
         <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W11" t="n">
         <v>1.2</v>
@@ -3257,7 +3257,7 @@
         <v>4.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
         <v>18.5</v>
@@ -3269,7 +3269,7 @@
         <v>5.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -3427,10 +3427,10 @@
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.55</v>
@@ -3442,16 +3442,16 @@
         <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V12" t="n">
         <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
@@ -3460,13 +3460,13 @@
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>13.5</v>
@@ -3481,7 +3481,7 @@
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
         <v>36</v>
@@ -3493,13 +3493,13 @@
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>20</v>
@@ -3508,7 +3508,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
@@ -3520,7 +3520,7 @@
         <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
@@ -3535,7 +3535,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>30</v>
@@ -3580,13 +3580,13 @@
         <v>5.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP12" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BR12" t="n">
         <v>25</v>
@@ -3598,7 +3598,7 @@
         <v>6.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV12" t="n">
         <v>21</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G13" t="n">
         <v>4.8</v>
@@ -3663,13 +3663,13 @@
         <v>2.42</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
@@ -3678,10 +3678,10 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
         <v>2.72</v>
@@ -3690,7 +3690,7 @@
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T13" t="n">
         <v>2.18</v>
@@ -3699,10 +3699,10 @@
         <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
@@ -3720,7 +3720,7 @@
         <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>14</v>
@@ -3732,7 +3732,7 @@
         <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH13" t="n">
         <v>30</v>
@@ -3756,7 +3756,7 @@
         <v>140</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
         <v>6.4</v>
@@ -3768,7 +3768,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3777,13 +3777,13 @@
         <v>5.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>13.5</v>
@@ -3792,25 +3792,25 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH13" t="n">
         <v>2.66</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H14" t="n">
         <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
@@ -3935,7 +3935,7 @@
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
         <v>2.3</v>
@@ -3947,7 +3947,7 @@
         <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.93</v>
@@ -3956,7 +3956,7 @@
         <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
@@ -3971,7 +3971,7 @@
         <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
@@ -3983,10 +3983,10 @@
         <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -3995,7 +3995,7 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK14" t="n">
         <v>34</v>
@@ -4022,10 +4022,10 @@
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -4046,7 +4046,7 @@
         <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB14" t="n">
         <v>4.7</v>
@@ -4058,13 +4058,13 @@
         <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH14" t="n">
         <v>2.96</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -4162,25 +4162,25 @@
         <v>3.55</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J15" t="n">
         <v>2.84</v>
       </c>
       <c r="K15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N15" t="n">
         <v>2.28</v>
@@ -4189,16 +4189,16 @@
         <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
         <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T15" t="n">
         <v>2.26</v>
@@ -4207,10 +4207,10 @@
         <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X15" t="n">
         <v>8</v>
@@ -4222,25 +4222,25 @@
         <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
         <v>120</v>
@@ -4261,7 +4261,7 @@
         <v>300</v>
       </c>
       <c r="AN15" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4270,58 +4270,58 @@
         <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
         <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>19.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC15" t="n">
+      <c r="BF15" t="n">
         <v>8</v>
       </c>
-      <c r="BD15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BI15" t="n">
         <v>2.12</v>
@@ -4339,13 +4339,13 @@
         <v>10.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO15" t="n">
         <v>5.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BQ15" t="n">
         <v>8.800000000000001</v>
@@ -4354,7 +4354,7 @@
         <v>75</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT15" t="n">
         <v>5.3</v>
@@ -4366,23 +4366,23 @@
         <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
         <v>70</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -4413,148 +4413,148 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.86</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.79</v>
-      </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
         <v>19.5</v>
       </c>
-      <c r="Z16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH16" t="n">
+      <c r="AO16" t="n">
         <v>65</v>
       </c>
-      <c r="AI16" t="n">
-        <v>410</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>590</v>
-      </c>
       <c r="AP16" t="n">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
         <v>18.5</v>
@@ -4563,16 +4563,16 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
         <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BH16" t="n">
         <v>4.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,10 +881,10 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
@@ -896,127 +896,127 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
         <v>3.35</v>
@@ -1165,118 +1165,118 @@
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AL3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="n">
         <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
         <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
         <v>2.86</v>
@@ -1386,7 +1386,7 @@
         <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
         <v>2.48</v>
@@ -1419,16 +1419,16 @@
         <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="n">
         <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AA4" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
         <v>7.6</v>
@@ -1437,55 +1437,55 @@
         <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
         <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>6</v>
@@ -1494,7 +1494,7 @@
         <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1506,25 +1506,25 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
@@ -1536,7 +1536,7 @@
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP4" t="n">
         <v>22</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="n">
         <v>3.2</v>
@@ -1631,10 +1631,10 @@
         <v>3.45</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1649,22 +1649,22 @@
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1673,112 +1673,112 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
         <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
         <v>36</v>
       </c>
-      <c r="AM5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>970</v>
-      </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="AQ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X6" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6" t="n">
         <v>2.48</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AV6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="BC6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
         <v>2.78</v>
@@ -2136,7 +2136,7 @@
         <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2151,16 +2151,16 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
@@ -2172,121 +2172,121 @@
         <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
         <v>36</v>
       </c>
-      <c r="AM7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
       </c>
       <c r="AV7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>14</v>
-      </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2298,13 +2298,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,13 +2316,13 @@
         <v>20</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
@@ -2334,23 +2334,23 @@
         <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
         <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2408,7 +2408,7 @@
         <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>2.32</v>
@@ -2417,7 +2417,7 @@
         <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
         <v>2.78</v>
@@ -2426,37 +2426,37 @@
         <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>22</v>
@@ -2468,49 +2468,49 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX8" t="n">
         <v>17.5</v>
@@ -2519,25 +2519,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BB8" t="n">
         <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG8" t="n">
         <v>15.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -2641,10 +2641,10 @@
         <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I9" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="J9" t="n">
         <v>3.55</v>
@@ -2677,19 +2677,19 @@
         <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
         <v>1.54</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
         <v>15</v>
@@ -2698,7 +2698,7 @@
         <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AB9" t="n">
         <v>14.5</v>
@@ -2725,19 +2725,19 @@
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
         <v>20</v>
@@ -2752,7 +2752,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
         <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
@@ -2776,19 +2776,19 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
         <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
@@ -2910,19 +2910,19 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
@@ -2934,37 +2934,37 @@
         <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2973,82 +2973,82 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU10" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AV10" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I11" t="n">
         <v>2.12</v>
@@ -3203,13 +3203,13 @@
         <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
         <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
         <v>9.199999999999999</v>
@@ -3218,7 +3218,7 @@
         <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
         <v>48</v>
@@ -3230,31 +3230,31 @@
         <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AL11" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AM11" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
@@ -3266,16 +3266,16 @@
         <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
         <v>17</v>
@@ -3284,22 +3284,22 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
         <v>21</v>
@@ -3308,7 +3308,7 @@
         <v>2.64</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -3400,58 +3400,58 @@
         <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="U12" t="n">
         <v>2.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
@@ -3460,19 +3460,19 @@
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF12" t="n">
         <v>19.5</v>
@@ -3481,43 +3481,43 @@
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ12" t="n">
         <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>40</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
         <v>8.4</v>
@@ -3535,7 +3535,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
         <v>30</v>
@@ -3568,7 +3568,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>3.8</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="n">
         <v>2.2</v>
@@ -3672,13 +3672,13 @@
         <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P13" t="n">
         <v>1.49</v>
@@ -3711,13 +3711,13 @@
         <v>7.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
         <v>7.6</v>
@@ -3726,10 +3726,10 @@
         <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
         <v>18.5</v>
@@ -3741,19 +3741,19 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>85</v>
       </c>
       <c r="AL13" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM13" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="AO13" t="n">
         <v>38</v>
@@ -3768,7 +3768,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX13" t="n">
         <v>20</v>
@@ -3792,25 +3792,25 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>2.66</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
         <v>3.5</v>
@@ -3971,7 +3971,7 @@
         <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
@@ -3980,7 +3980,7 @@
         <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
         <v>16</v>
@@ -3992,7 +3992,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
@@ -4004,7 +4004,7 @@
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>32</v>
@@ -4022,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
@@ -4034,7 +4034,7 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -4046,25 +4046,25 @@
         <v>18</v>
       </c>
       <c r="BA14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB14" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH14" t="n">
         <v>2.96</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>3.55</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
         <v>2.84</v>
@@ -4183,13 +4183,13 @@
         <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
         <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
@@ -4201,7 +4201,7 @@
         <v>6.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
@@ -4210,22 +4210,22 @@
         <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
         <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
@@ -4237,7 +4237,7 @@
         <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>18.5</v>
@@ -4246,22 +4246,22 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="n">
         <v>100</v>
       </c>
       <c r="AK15" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM15" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4276,7 +4276,7 @@
         <v>11.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AT15" t="n">
         <v>7.6</v>
@@ -4300,31 +4300,31 @@
         <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BH15" t="n">
         <v>2.54</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="G16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4461,10 +4461,10 @@
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X16" t="n">
         <v>18.5</v>
@@ -4488,13 +4488,13 @@
         <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
         <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
@@ -4506,7 +4506,7 @@
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>40</v>
@@ -4518,7 +4518,7 @@
         <v>19.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
         <v>11.5</v>
@@ -4527,7 +4527,7 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
@@ -4542,7 +4542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -4557,7 +4557,7 @@
         <v>38</v>
       </c>
       <c r="BB16" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
@@ -4584,59 +4584,59 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -860,13 +860,13 @@
         <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>2.12</v>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
         <v>2.8</v>
@@ -881,10 +881,10 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
         <v>1.83</v>
@@ -911,40 +911,40 @@
         <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE2" t="n">
         <v>500</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>290</v>
       </c>
       <c r="AF2" t="n">
         <v>500</v>
       </c>
       <c r="AG2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI2" t="n">
         <v>500</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>390</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
@@ -962,13 +962,13 @@
         <v>500</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AR2" t="n">
         <v>1.21</v>
@@ -992,7 +992,7 @@
         <v>1.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.2</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
         <v>2.42</v>
@@ -1129,16 +1129,16 @@
         <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
         <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.55</v>
@@ -1150,7 +1150,7 @@
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
@@ -1165,10 +1165,10 @@
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z3" t="n">
         <v>14</v>
@@ -1189,7 +1189,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AG3" t="n">
         <v>18</v>
@@ -1198,7 +1198,7 @@
         <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
@@ -1219,7 +1219,7 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.4</v>
@@ -1228,7 +1228,7 @@
         <v>6.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1237,49 +1237,49 @@
         <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AW3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6</v>
-      </c>
       <c r="BA3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH3" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
         <v>5.7</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BN3" t="n">
         <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>2.16</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.2</v>
       </c>
       <c r="BT3" t="n">
         <v>5.1</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>22</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1619,40 +1619,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
@@ -1661,10 +1661,10 @@
         <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1688,7 +1688,7 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1727,7 +1727,7 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AQ5" t="n">
         <v>8.4</v>
@@ -1736,7 +1736,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
         <v>8.4</v>
@@ -1757,28 +1757,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1802,13 +1802,13 @@
         <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,13 +1820,13 @@
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>9.6</v>
@@ -1897,7 +1897,7 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
@@ -1915,16 +1915,16 @@
         <v>2.58</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U6" t="n">
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -2032,7 +2032,7 @@
         <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
         <v>2.78</v>
@@ -2136,7 +2136,7 @@
         <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2151,37 +2151,37 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T7" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
         <v>15</v>
@@ -2232,7 +2232,7 @@
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
@@ -2265,10 +2265,10 @@
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7" t="n">
         <v>34</v>
@@ -2277,7 +2277,7 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
         <v>55</v>
@@ -2289,22 +2289,22 @@
         <v>16</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,41 +2316,41 @@
         <v>20</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
         <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2399,124 +2399,124 @@
         <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
         <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
@@ -2534,77 +2534,77 @@
         <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
         <v>16</v>
       </c>
       <c r="BG8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>21</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
         <v>28</v>
@@ -2734,7 +2734,7 @@
         <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
         <v>20</v>
@@ -2752,7 +2752,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2776,10 +2776,10 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
         <v>13</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
         <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
@@ -2922,7 +2922,7 @@
         <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
@@ -2940,7 +2940,7 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2973,7 +2973,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -3018,7 +3018,7 @@
         <v>5.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3039,7 +3039,7 @@
         <v>2.04</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="BE10" t="n">
         <v>2.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I11" t="n">
         <v>2.12</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="n">
         <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -3421,28 +3421,28 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
         <v>1.5</v>
@@ -3451,25 +3451,25 @@
         <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>28</v>
@@ -3487,40 +3487,40 @@
         <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>15</v>
-      </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>40</v>
       </c>
       <c r="AT12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
@@ -3550,13 +3550,13 @@
         <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF12" t="n">
         <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
@@ -3568,7 +3568,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>2.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J13" t="n">
         <v>2.98</v>
@@ -3717,7 +3717,7 @@
         <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
         <v>7.6</v>
@@ -3735,7 +3735,7 @@
         <v>18.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>80</v>
@@ -3792,22 +3792,22 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
         <v>6.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -3920,7 +3920,7 @@
         <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>1.44</v>
@@ -3929,13 +3929,13 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
         <v>2.3</v>
@@ -3944,13 +3944,13 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
         <v>1.36</v>
@@ -3995,13 +3995,13 @@
         <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4022,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
@@ -4034,7 +4034,7 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -4043,28 +4043,28 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH14" t="n">
         <v>2.96</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>2.54</v>
       </c>
       <c r="J15" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K15" t="n">
         <v>3.1</v>
@@ -4183,13 +4183,13 @@
         <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
         <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
@@ -4306,7 +4306,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>9.4</v>
@@ -4342,7 +4342,7 @@
         <v>7.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP15" t="n">
         <v>44</v>
@@ -4360,7 +4360,7 @@
         <v>5.3</v>
       </c>
       <c r="BU15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BV15" t="n">
         <v>25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
         <v>3.45</v>
@@ -4425,10 +4425,10 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,10 +4437,10 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
         <v>1.9</v>
@@ -4458,22 +4458,22 @@
         <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
         <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X16" t="n">
         <v>18.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
         <v>100</v>
@@ -4485,28 +4485,28 @@
         <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
         <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
         <v>40</v>
@@ -4527,10 +4527,10 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>7.2</v>
@@ -4542,7 +4542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -4563,16 +4563,16 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>38</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>4.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>8.800000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X2" t="n">
         <v>950</v>
@@ -926,7 +926,7 @@
         <v>950</v>
       </c>
       <c r="AC2" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
@@ -959,22 +959,22 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -983,34 +983,34 @@
         <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
@@ -1276,7 +1276,7 @@
         <v>2.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H4" t="n">
         <v>3.55</v>
@@ -1407,7 +1407,7 @@
         <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
         <v>1.73</v>
@@ -1416,7 +1416,7 @@
         <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
         <v>9</v>
@@ -1548,7 +1548,7 @@
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
         <v>22</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
         <v>3.05</v>
@@ -1631,7 +1631,7 @@
         <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
@@ -1676,7 +1676,7 @@
         <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1691,7 +1691,7 @@
         <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
@@ -1706,7 +1706,7 @@
         <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
@@ -1727,7 +1727,7 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>8.4</v>
@@ -1766,7 +1766,7 @@
         <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
         <v>5.4</v>
@@ -1775,7 +1775,7 @@
         <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,10 +1897,10 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
         <v>2.16</v>
@@ -1921,16 +1921,16 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
         <v>100</v>
@@ -1981,7 +1981,7 @@
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AQ6" t="n">
         <v>11.5</v>
@@ -1990,13 +1990,13 @@
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AV6" t="n">
         <v>9.4</v>
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BF6" t="n">
         <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
         <v>2.78</v>
@@ -2136,7 +2136,7 @@
         <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2151,31 +2151,31 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
         <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.55</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
@@ -2196,7 +2196,7 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
@@ -2211,7 +2211,7 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AI7" t="n">
         <v>70</v>
@@ -2232,7 +2232,7 @@
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
@@ -2250,7 +2250,7 @@
         <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -2259,16 +2259,16 @@
         <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>34</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
         <v>2.6</v>
@@ -2423,16 +2423,16 @@
         <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
@@ -2465,13 +2465,13 @@
         <v>14.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI8" t="n">
         <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
         <v>16</v>
@@ -2546,7 +2546,7 @@
         <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G9" t="n">
         <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>3.8</v>
@@ -2674,7 +2674,7 @@
         <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T9" t="n">
         <v>1.61</v>
@@ -2683,7 +2683,7 @@
         <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
         <v>1.54</v>
@@ -2692,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>21</v>
@@ -2707,10 +2707,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF9" t="n">
         <v>21</v>
@@ -2722,10 +2722,10 @@
         <v>15.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK9" t="n">
         <v>28</v>
@@ -2734,13 +2734,13 @@
         <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN9" t="n">
         <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP9" t="n">
         <v>13.5</v>
@@ -2752,13 +2752,13 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2776,19 +2776,19 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
         <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
         <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
         <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
         <v>5.5</v>
@@ -3000,16 +3000,16 @@
         <v>4.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
         <v>3.9</v>
@@ -3018,37 +3018,37 @@
         <v>5.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BE10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF10" t="n">
         <v>2.1</v>
       </c>
-      <c r="BF10" t="n">
-        <v>2</v>
-      </c>
       <c r="BG10" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -3155,37 +3155,37 @@
         <v>2.12</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
         <v>1.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
         <v>1.6</v>
@@ -3200,13 +3200,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="Z11" t="n">
         <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB11" t="n">
         <v>13</v>
@@ -3221,13 +3221,13 @@
         <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AG11" t="n">
         <v>29</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3284,46 +3284,46 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
         <v>21</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO11" t="n">
         <v>4.9</v>
@@ -3344,7 +3344,7 @@
         <v>4.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV11" t="n">
         <v>18</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -3421,7 +3421,7 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
@@ -3430,13 +3430,13 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
         <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
         <v>1.59</v>
@@ -3529,7 +3529,7 @@
         <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G13" t="n">
         <v>4.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
         <v>1.13</v>
@@ -3678,13 +3678,13 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
         <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -3702,7 +3702,7 @@
         <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
@@ -3720,7 +3720,7 @@
         <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD13" t="n">
         <v>14</v>
@@ -3792,28 +3792,28 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC13" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC13" t="n">
-        <v>7</v>
-      </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
         <v>6.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI13" t="n">
         <v>2.24</v>
@@ -3822,7 +3822,7 @@
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,13 +3834,13 @@
         <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP13" t="n">
         <v>44</v>
       </c>
       <c r="BQ13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3858,7 +3858,7 @@
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX13" t="n">
         <v>48</v>
@@ -3870,11 +3870,11 @@
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -3941,7 +3941,7 @@
         <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
         <v>4.6</v>
@@ -3983,10 +3983,10 @@
         <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -4022,22 +4022,22 @@
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>5.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -4046,25 +4046,25 @@
         <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="n">
         <v>2.96</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
         <v>3.9</v>
@@ -4300,10 +4300,10 @@
         <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC15" t="n">
         <v>28</v>
@@ -4342,7 +4342,7 @@
         <v>7.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP15" t="n">
         <v>44</v>
@@ -4360,7 +4360,7 @@
         <v>5.3</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BV15" t="n">
         <v>25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
         <v>1.87</v>
       </c>
       <c r="X16" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y16" t="n">
         <v>950</v>
@@ -4482,7 +4482,7 @@
         <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>950</v>
@@ -4497,7 +4497,7 @@
         <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
@@ -4515,7 +4515,7 @@
         <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
@@ -4524,31 +4524,31 @@
         <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
@@ -4560,19 +4560,19 @@
         <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="n">
         <v>4.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,64 +857,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.05</v>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S2" t="n">
         <v>4.2</v>
       </c>
-      <c r="J2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y2" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,13 +923,13 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -938,7 +938,7 @@
         <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>950</v>
+        <v>160</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -950,7 +950,7 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -968,119 +968,119 @@
         <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.28</v>
+        <v>5.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.29</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.28</v>
+        <v>7.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.28</v>
+        <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>2.84</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
         <v>3.35</v>
@@ -1135,34 +1135,34 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
         <v>9.199999999999999</v>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
@@ -1186,13 +1186,13 @@
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>75</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
@@ -1210,13 +1210,13 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP3" t="n">
         <v>4.6</v>
@@ -1237,13 +1237,13 @@
         <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW3" t="n">
         <v>7.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>6</v>
@@ -1252,10 +1252,10 @@
         <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC3" t="n">
         <v>8.199999999999999</v>
@@ -1264,77 +1264,77 @@
         <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>2.22</v>
       </c>
-      <c r="BN3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BT3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV3" t="n">
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
         <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>11</v>
@@ -1434,31 +1434,31 @@
         <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
         <v>460</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL4" t="n">
         <v>460</v>
@@ -1467,22 +1467,22 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1491,58 +1491,58 @@
         <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
         <v>9</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ4" t="n">
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
@@ -1551,7 +1551,7 @@
         <v>3.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ4" t="n">
         <v>7.2</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>7.2</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1622,43 +1622,43 @@
         <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
         <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1673,7 +1673,7 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
@@ -1688,7 +1688,7 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1697,13 +1697,13 @@
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>150</v>
@@ -1712,13 +1712,13 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
         <v>36</v>
@@ -1727,7 +1727,7 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>8.4</v>
@@ -1736,7 +1736,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
         <v>8.4</v>
@@ -1760,25 +1760,25 @@
         <v>8.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,29 +1820,29 @@
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>3.9</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>3.85</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
         <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
         <v>4.1</v>
       </c>
       <c r="J6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.9</v>
       </c>
-      <c r="K6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
         <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>100</v>
@@ -1939,100 +1939,100 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
         <v>22</v>
       </c>
-      <c r="AI6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>27</v>
-      </c>
       <c r="AL6" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.84</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.1</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.88</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -2130,43 +2130,43 @@
         <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
@@ -2175,10 +2175,10 @@
         <v>2.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2190,7 +2190,7 @@
         <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
@@ -2202,7 +2202,7 @@
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
@@ -2214,22 +2214,22 @@
         <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="AO7" t="n">
         <v>19.5</v>
@@ -2241,13 +2241,13 @@
         <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
         <v>36</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>7.8</v>
@@ -2268,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
         <v>34</v>
@@ -2277,16 +2277,16 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
         <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
         <v>4.1</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2313,16 +2313,16 @@
         <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
@@ -2334,23 +2334,23 @@
         <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2399,40 +2399,40 @@
         <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
@@ -2447,7 +2447,7 @@
         <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC8" t="n">
         <v>8.800000000000001</v>
@@ -2459,10 +2459,10 @@
         <v>25</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
         <v>14.5</v>
@@ -2471,13 +2471,13 @@
         <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
         <v>200</v>
@@ -2489,25 +2489,25 @@
         <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
         <v>20</v>
@@ -2519,31 +2519,31 @@
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BF8" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
         <v>3.1</v>
@@ -2552,37 +2552,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP8" t="n">
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>19</v>
@@ -2594,17 +2594,17 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G9" t="n">
         <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
         <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>22</v>
@@ -2701,10 +2701,10 @@
         <v>85</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
@@ -2713,16 +2713,16 @@
         <v>28</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
         <v>85</v>
@@ -2731,16 +2731,16 @@
         <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
         <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP9" t="n">
         <v>13.5</v>
@@ -2749,13 +2749,13 @@
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2764,31 +2764,31 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
@@ -2806,31 +2806,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
         <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
         <v>6.2</v>
@@ -2839,26 +2839,26 @@
         <v>4.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
         <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T10" t="n">
         <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2955,10 +2955,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2997,28 +2997,28 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT10" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>4</v>
       </c>
-      <c r="AU10" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AV10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3027,92 +3027,92 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.08</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -3143,46 +3143,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="I11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T11" t="n">
         <v>2.36</v>
@@ -3191,13 +3191,13 @@
         <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y11" t="n">
         <v>6.2</v>
@@ -3206,7 +3206,7 @@
         <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
         <v>13</v>
@@ -3215,7 +3215,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
         <v>34</v>
@@ -3224,10 +3224,10 @@
         <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3248,125 +3248,125 @@
         <v>700</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>4.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BV11" t="n">
         <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G12" t="n">
         <v>2.48</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -3418,25 +3418,25 @@
         <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
         <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
         <v>1.59</v>
@@ -3445,13 +3445,13 @@
         <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
@@ -3466,7 +3466,7 @@
         <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
@@ -3499,13 +3499,13 @@
         <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
@@ -3514,7 +3514,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
@@ -3556,13 +3556,13 @@
         <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN12" t="n">
         <v>5.7</v>
@@ -3592,7 +3592,7 @@
         <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
         <v>6.4</v>
@@ -3610,17 +3610,17 @@
         <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
         <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="I13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
@@ -3675,7 +3675,7 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O13" t="n">
         <v>1.58</v>
@@ -3687,28 +3687,28 @@
         <v>2.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
         <v>5.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>13.5</v>
@@ -3720,7 +3720,7 @@
         <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
         <v>14</v>
@@ -3729,13 +3729,13 @@
         <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>80</v>
@@ -3744,103 +3744,103 @@
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
         <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>3.95</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3852,16 +3852,16 @@
         <v>4.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV13" t="n">
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
         <v>8.800000000000001</v>
@@ -3870,11 +3870,11 @@
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -3908,43 +3908,43 @@
         <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
         <v>1.97</v>
@@ -3956,10 +3956,10 @@
         <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3968,19 +3968,19 @@
         <v>29</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
         <v>8.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
         <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
         <v>15.5</v>
@@ -3989,7 +3989,7 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>170</v>
@@ -4013,7 +4013,7 @@
         <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -4022,19 +4022,19 @@
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>11.5</v>
@@ -4043,49 +4043,49 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO14" t="n">
         <v>4</v>
@@ -4094,41 +4094,41 @@
         <v>19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT14" t="n">
         <v>6.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
         <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>12</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>11</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I15" t="n">
         <v>2.54</v>
@@ -4174,46 +4174,46 @@
         <v>2.88</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y15" t="n">
         <v>7</v>
@@ -4297,31 +4297,31 @@
         <v>15.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC15" t="n">
         <v>28</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF15" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
         <v>40</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BI15" t="n">
         <v>2.1</v>
@@ -4330,31 +4330,31 @@
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP15" t="n">
         <v>44</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT15" t="n">
         <v>5.3</v>
@@ -4366,23 +4366,23 @@
         <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>70</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -4413,58 +4413,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
         <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X16" t="n">
         <v>17.5</v>
@@ -4473,25 +4473,25 @@
         <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA16" t="n">
         <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>950</v>
@@ -4503,37 +4503,37 @@
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
@@ -4542,10 +4542,10 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>8.6</v>
@@ -4554,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4563,80 +4563,80 @@
         <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
         <v>4.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
@@ -899,16 +899,16 @@
         <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
         <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
         <v>500</v>
@@ -938,7 +938,7 @@
         <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -968,13 +968,13 @@
         <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.96</v>
+        <v>2.14</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -986,7 +986,7 @@
         <v>7.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,16 +998,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
         <v>5</v>
@@ -1016,13 +1016,13 @@
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.84</v>
+        <v>1.85</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="BN2" t="n">
         <v>5.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1052,35 +1052,35 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BT2" t="n">
         <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.58</v>
+        <v>2.98</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1114,55 +1114,55 @@
         <v>3.55</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>9.199999999999999</v>
@@ -1240,7 +1240,7 @@
         <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>6.8</v>
@@ -1249,7 +1249,7 @@
         <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
@@ -1273,16 +1273,16 @@
         <v>7.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1312,13 +1312,13 @@
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV3" t="n">
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
@@ -1386,7 +1386,7 @@
         <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
         <v>2.62</v>
@@ -1407,7 +1407,7 @@
         <v>5.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
         <v>1.76</v>
@@ -1452,10 +1452,10 @@
         <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
         <v>95</v>
@@ -1479,7 +1479,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
         <v>9</v>
@@ -1491,10 +1491,10 @@
         <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
         <v>9</v>
@@ -1518,7 +1518,7 @@
         <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
         <v>7.8</v>
@@ -1554,13 +1554,13 @@
         <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>7.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
         <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
         <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1643,7 +1643,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1652,10 +1652,10 @@
         <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
         <v>3.05</v>
@@ -1664,7 +1664,7 @@
         <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1673,7 +1673,7 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
@@ -1688,7 +1688,7 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1703,7 +1703,7 @@
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>150</v>
@@ -1724,10 +1724,10 @@
         <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>8.4</v>
@@ -1736,19 +1736,19 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
         <v>8.4</v>
@@ -1757,46 +1757,46 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>3.95</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
         <v>1.67</v>
@@ -1915,10 +1915,10 @@
         <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V6" t="n">
         <v>1.32</v>
@@ -1927,176 +1927,176 @@
         <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
         <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN6" t="n">
         <v>10.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="BN6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
         <v>2.82</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
@@ -2169,10 +2169,10 @@
         <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
         <v>1.54</v>
@@ -2202,7 +2202,7 @@
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
@@ -2214,7 +2214,7 @@
         <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
         <v>40</v>
@@ -2229,7 +2229,7 @@
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>19.5</v>
@@ -2247,7 +2247,7 @@
         <v>36</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
         <v>7.8</v>
@@ -2283,7 +2283,7 @@
         <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="BG7" t="n">
         <v>17</v>
@@ -2292,7 +2292,7 @@
         <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2408,7 +2408,7 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
         <v>2.3</v>
@@ -2432,31 +2432,31 @@
         <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB8" t="n">
         <v>16.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>24</v>
@@ -2471,7 +2471,7 @@
         <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2480,22 +2480,22 @@
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
         <v>30</v>
@@ -2522,13 +2522,13 @@
         <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
         <v>25</v>
       </c>
       <c r="BC8" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
         <v>29</v>
@@ -2540,25 +2540,25 @@
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2567,34 +2567,34 @@
         <v>5.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
         <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>20</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
         <v>2.66</v>
@@ -2659,40 +2659,40 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
         <v>21</v>
@@ -2704,16 +2704,16 @@
         <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
@@ -2737,25 +2737,25 @@
         <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT9" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2764,55 +2764,55 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX9" t="n">
         <v>18</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
         <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF9" t="n">
         <v>16.5</v>
       </c>
-      <c r="BE9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>14</v>
-      </c>
       <c r="BG9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="n">
         <v>4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>6.2</v>
@@ -2821,16 +2821,16 @@
         <v>4.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
         <v>6.2</v>
@@ -2842,23 +2842,23 @@
         <v>19</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -2889,40 +2889,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
         <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="L10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
         <v>2.52</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
@@ -2931,22 +2931,22 @@
         <v>5.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,10 +2955,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2979,7 +2979,7 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2991,34 +2991,34 @@
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU10" t="n">
         <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.8</v>
+        <v>2.98</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3027,40 +3027,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="BG10" t="n">
         <v>5.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.39</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,47 +3072,47 @@
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.39</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>5.9</v>
@@ -3158,7 +3158,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.66</v>
@@ -3170,19 +3170,19 @@
         <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
         <v>1.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
         <v>2.36</v>
@@ -3197,13 +3197,13 @@
         <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="n">
         <v>6.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
         <v>75</v>
@@ -3212,19 +3212,19 @@
         <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
         <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AH11" t="n">
         <v>85</v>
@@ -3251,16 +3251,16 @@
         <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -3272,37 +3272,37 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="n">
         <v>2.58</v>
@@ -3320,13 +3320,13 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3347,7 +3347,7 @@
         <v>3.45</v>
       </c>
       <c r="BV11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW11" t="n">
         <v>7.4</v>
@@ -3362,11 +3362,11 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G12" t="n">
         <v>2.48</v>
       </c>
       <c r="H12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -3421,7 +3421,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
@@ -3439,10 +3439,10 @@
         <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
         <v>1.48</v>
@@ -3460,13 +3460,13 @@
         <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AB12" t="n">
         <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
@@ -3487,7 +3487,7 @@
         <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
@@ -3502,7 +3502,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
@@ -3511,10 +3511,10 @@
         <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
@@ -3523,13 +3523,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
         <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
@@ -3553,10 +3553,10 @@
         <v>55</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
         <v>13</v>
@@ -3660,7 +3660,7 @@
         <v>1.99</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
         <v>2.56</v>
@@ -3675,16 +3675,16 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
         <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
@@ -3708,13 +3708,13 @@
         <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z13" t="n">
         <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
         <v>10.5</v>
@@ -3732,19 +3732,19 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AL13" t="n">
         <v>540</v>
@@ -3756,7 +3756,7 @@
         <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AP13" t="n">
         <v>4.4</v>
@@ -3765,10 +3765,10 @@
         <v>3.85</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3780,40 +3780,40 @@
         <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI13" t="n">
         <v>2.26</v>
@@ -3822,31 +3822,31 @@
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>3.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BT13" t="n">
         <v>4.9</v>
@@ -3858,23 +3858,23 @@
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BZ13" t="n">
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -3923,7 +3923,7 @@
         <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
@@ -3935,10 +3935,10 @@
         <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
@@ -3947,31 +3947,31 @@
         <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="V14" t="n">
         <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
@@ -4016,25 +4016,25 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
         <v>11.5</v>
@@ -4046,25 +4046,25 @@
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE14" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>9</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="n">
         <v>2.92</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>3.95</v>
       </c>
       <c r="H15" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
         <v>2.54</v>
@@ -4174,25 +4174,25 @@
         <v>2.88</v>
       </c>
       <c r="K15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P15" t="n">
         <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
         <v>1.15</v>
@@ -4201,16 +4201,16 @@
         <v>7.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>7.4</v>
@@ -4222,13 +4222,13 @@
         <v>14.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD15" t="n">
         <v>14</v>
@@ -4237,7 +4237,7 @@
         <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>18.5</v>
@@ -4246,16 +4246,16 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>190</v>
+        <v>460</v>
       </c>
       <c r="AJ15" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
@@ -4300,22 +4300,22 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
         <v>28</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
         <v>40</v>
@@ -4330,13 +4330,13 @@
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN15" t="n">
         <v>7</v>
@@ -4348,41 +4348,41 @@
         <v>44</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV15" t="n">
         <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX15" t="n">
         <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>70</v>
       </c>
       <c r="CA15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
         <v>2.1</v>
@@ -4425,40 +4425,40 @@
         <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
         <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
         <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
         <v>1.31</v>
@@ -4467,10 +4467,10 @@
         <v>1.9</v>
       </c>
       <c r="X16" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
         <v>30</v>
@@ -4485,7 +4485,7 @@
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
@@ -4494,7 +4494,7 @@
         <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
@@ -4515,7 +4515,7 @@
         <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO16" t="n">
         <v>55</v>
@@ -4527,13 +4527,13 @@
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
@@ -4542,7 +4542,7 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -4551,92 +4551,92 @@
         <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
         <v>12.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,64 +857,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,10 +923,10 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -950,7 +950,7 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -962,31 +962,31 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP2" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
         <v>7.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,89 +998,89 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
         <v>7.8</v>
       </c>
       <c r="BD2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>5.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
         <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.98</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.55</v>
@@ -1135,31 +1135,31 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T3" t="n">
         <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W3" t="n">
         <v>1.31</v>
@@ -1168,7 +1168,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z3" t="n">
         <v>14</v>
@@ -1192,7 +1192,7 @@
         <v>75</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
@@ -1210,70 +1210,70 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
         <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BD3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI3" t="n">
         <v>2.5</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.18</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
@@ -1318,23 +1318,23 @@
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
         <v>90</v>
@@ -1431,34 +1431,34 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>460</v>
@@ -1473,76 +1473,76 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
         <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
         <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
@@ -1551,16 +1551,16 @@
         <v>3.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>7.2</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I5" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
@@ -1652,19 +1652,19 @@
         <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1673,176 +1673,176 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
         <v>13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD5" t="n">
         <v>16</v>
       </c>
-      <c r="AX5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8</v>
-      </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.99</v>
+        <v>2.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1879,31 +1879,31 @@
         <v>2.08</v>
       </c>
       <c r="H6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.85</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>1.67</v>
@@ -1912,43 +1912,43 @@
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
         <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
         <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF6" t="n">
         <v>15</v>
@@ -1957,58 +1957,58 @@
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
         <v>10.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR6" t="n">
         <v>28</v>
       </c>
       <c r="AS6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>34</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
@@ -2017,7 +2017,7 @@
         <v>38</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -2026,28 +2026,28 @@
         <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM6" t="n">
         <v>12.5</v>
@@ -2056,7 +2056,7 @@
         <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
         <v>13.5</v>
@@ -2065,7 +2065,7 @@
         <v>7</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS6" t="n">
         <v>9</v>
@@ -2080,7 +2080,7 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2089,14 +2089,14 @@
         <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA6" t="n">
         <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.7</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.74</v>
-      </c>
       <c r="I7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2154,37 +2154,37 @@
         <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.58</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
@@ -2196,16 +2196,16 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -2229,22 +2229,22 @@
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT7" t="n">
         <v>12.5</v>
@@ -2268,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
         <v>34</v>
@@ -2277,80 +2277,80 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
         <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
         <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP7" t="n">
         <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>20</v>
       </c>
       <c r="CA7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2399,70 +2399,70 @@
         <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
         <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
         <v>42</v>
       </c>
       <c r="AB8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8" t="n">
         <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>14.5</v>
@@ -2474,34 +2474,34 @@
         <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
         <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
         <v>7.4</v>
@@ -2510,101 +2510,101 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
         <v>29</v>
       </c>
       <c r="BE8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.34</v>
@@ -2674,22 +2674,22 @@
         <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
         <v>15</v>
@@ -2698,10 +2698,10 @@
         <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2713,10 +2713,10 @@
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2728,22 +2728,22 @@
         <v>85</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2752,10 +2752,10 @@
         <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2764,19 +2764,19 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX9" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
         <v>32</v>
@@ -2785,19 +2785,19 @@
         <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE9" t="n">
         <v>30</v>
       </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
         <v>3.15</v>
@@ -2806,59 +2806,59 @@
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
         <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV9" t="n">
         <v>20</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BW9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY9" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>20</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
         <v>3.9</v>
@@ -2904,16 +2904,16 @@
         <v>2.64</v>
       </c>
       <c r="K10" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
         <v>1.58</v>
@@ -2922,7 +2922,7 @@
         <v>1.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
@@ -2937,7 +2937,7 @@
         <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
         <v>1.54</v>
@@ -2946,7 +2946,7 @@
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
         <v>42</v>
@@ -2994,64 +2994,64 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>3.15</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.24</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.24</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.92</v>
+        <v>2.14</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>2.28</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI10" t="n">
         <v>2.2</v>
@@ -3060,7 +3060,7 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,16 +3069,16 @@
         <v>1.39</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3090,7 +3090,7 @@
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,17 +3102,17 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>5.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.66</v>
@@ -3173,7 +3173,7 @@
         <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
@@ -3191,7 +3191,7 @@
         <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W11" t="n">
         <v>1.21</v>
@@ -3203,10 +3203,10 @@
         <v>6.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AB11" t="n">
         <v>13</v>
@@ -3224,7 +3224,7 @@
         <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AH11" t="n">
         <v>85</v>
@@ -3233,7 +3233,7 @@
         <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AK11" t="n">
         <v>700</v>
@@ -3248,7 +3248,7 @@
         <v>700</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
         <v>6.4</v>
@@ -3257,7 +3257,7 @@
         <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS11" t="n">
         <v>21</v>
@@ -3275,37 +3275,37 @@
         <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE11" t="n">
         <v>8.6</v>
       </c>
-      <c r="BD11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9</v>
-      </c>
       <c r="BF11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BI11" t="n">
         <v>2.14</v>
@@ -3314,59 +3314,59 @@
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
         <v>4.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -3427,7 +3427,7 @@
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
         <v>1.7</v>
@@ -3436,10 +3436,10 @@
         <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
         <v>2.56</v>
@@ -3448,19 +3448,19 @@
         <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
         <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
         <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
         <v>14</v>
@@ -3469,13 +3469,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -3496,22 +3496,22 @@
         <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>40</v>
@@ -3538,31 +3538,31 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
         <v>30</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
@@ -3574,53 +3574,53 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO12" t="n">
         <v>5.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="BT12" t="n">
         <v>6.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV12" t="n">
         <v>21</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12" t="n">
         <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3651,28 +3651,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>2.46</v>
       </c>
       <c r="J13" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
         <v>2.48</v>
@@ -3681,10 +3681,10 @@
         <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
@@ -3693,19 +3693,19 @@
         <v>5.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
         <v>1.27</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13" t="n">
         <v>7.2</v>
@@ -3729,10 +3729,10 @@
         <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -3744,7 +3744,7 @@
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="n">
         <v>540</v>
@@ -3753,128 +3753,128 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AO13" t="n">
         <v>90</v>
       </c>
       <c r="AP13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BT13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV13" t="n">
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
@@ -3926,19 +3926,19 @@
         <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
@@ -3947,34 +3947,34 @@
         <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
         <v>18</v>
@@ -3983,10 +3983,10 @@
         <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -3995,10 +3995,10 @@
         <v>170</v>
       </c>
       <c r="AJ14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK14" t="n">
         <v>34</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>32</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -4013,31 +4013,31 @@
         <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -4046,43 +4046,43 @@
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>2.92</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN14" t="n">
         <v>5</v>
@@ -4091,44 +4091,44 @@
         <v>4</v>
       </c>
       <c r="BP14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
         <v>12</v>
       </c>
-      <c r="BT14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>13</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>12</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I15" t="n">
         <v>2.54</v>
       </c>
       <c r="J15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
@@ -4183,7 +4183,7 @@
         <v>1.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.71</v>
@@ -4192,10 +4192,10 @@
         <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S15" t="n">
         <v>7.2</v>
@@ -4207,28 +4207,28 @@
         <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
         <v>14</v>
@@ -4237,7 +4237,7 @@
         <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>18.5</v>
@@ -4246,13 +4246,13 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>460</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="n">
         <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="n">
         <v>540</v>
@@ -4261,7 +4261,7 @@
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4270,119 +4270,119 @@
         <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF15" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH15" t="n">
         <v>2.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN15" t="n">
         <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP15" t="n">
         <v>44</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU15" t="n">
         <v>4.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>70</v>
       </c>
       <c r="CA15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.2</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
         <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.55</v>
+        <v>2.54</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.84</v>
+        <v>7.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.57</v>
+        <v>2.44</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.51</v>
@@ -881,79 +881,79 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
         <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
         <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
-        <v>85</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>60</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
         <v>13</v>
       </c>
-      <c r="AD2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>70</v>
-      </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -965,122 +965,122 @@
         <v>90</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT2" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.25</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO2" t="n">
         <v>4.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT2" t="n">
         <v>7</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J3" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
@@ -1138,7 +1138,7 @@
         <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
         <v>1.54</v>
@@ -1150,25 +1150,25 @@
         <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
         <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z3" t="n">
         <v>14</v>
@@ -1189,10 +1189,10 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
@@ -1219,13 +1219,13 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
         <v>11.5</v>
@@ -1252,25 +1252,25 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>2.76</v>
@@ -1282,40 +1282,40 @@
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>8.4</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
         <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.05</v>
@@ -1389,61 +1389,61 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
         <v>4.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1455,112 +1455,112 @@
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK4" t="n">
         <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK4" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF4" t="n">
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BG4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>7.2</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1649,22 +1649,22 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R5" t="n">
         <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1682,16 +1682,16 @@
         <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
@@ -1706,7 +1706,7 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ5" t="n">
         <v>48</v>
@@ -1718,7 +1718,7 @@
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
         <v>16.5</v>
@@ -1772,10 +1772,10 @@
         <v>16</v>
       </c>
       <c r="BE5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>24</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
@@ -1885,7 +1885,7 @@
         <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
@@ -1897,13 +1897,13 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
         <v>1.67</v>
@@ -1912,40 +1912,40 @@
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
         <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
         <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
         <v>38</v>
@@ -1960,7 +1960,7 @@
         <v>15.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1981,7 +1981,7 @@
         <v>30</v>
       </c>
       <c r="AP6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
         <v>17.5</v>
@@ -2026,28 +2026,28 @@
         <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM6" t="n">
         <v>12.5</v>
@@ -2056,7 +2056,7 @@
         <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
         <v>13.5</v>
@@ -2077,10 +2077,10 @@
         <v>5.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2089,14 +2089,14 @@
         <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA6" t="n">
         <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -2151,76 +2151,76 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
         <v>1.63</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
         <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -2229,52 +2229,52 @@
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
         <v>29</v>
@@ -2283,10 +2283,10 @@
         <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.85</v>
@@ -2304,25 +2304,25 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
@@ -2331,13 +2331,13 @@
         <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BW7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2405,7 +2405,7 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
@@ -2417,25 +2417,25 @@
         <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V8" t="n">
         <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
         <v>14.5</v>
@@ -2444,7 +2444,7 @@
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="n">
         <v>15</v>
@@ -2456,7 +2456,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AF8" t="n">
         <v>22</v>
@@ -2465,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>34</v>
@@ -2474,28 +2474,28 @@
         <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
         <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
         <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
         <v>32</v>
@@ -2504,16 +2504,16 @@
         <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
@@ -2522,25 +2522,25 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB8" t="n">
         <v>34</v>
       </c>
       <c r="BC8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH8" t="n">
         <v>3.95</v>
@@ -2558,7 +2558,7 @@
         <v>90</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2576,13 +2576,13 @@
         <v>30</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>19</v>
@@ -2591,10 +2591,10 @@
         <v>6.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>21</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
@@ -2677,13 +2677,13 @@
         <v>2.86</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
         <v>1.58</v>
@@ -2719,13 +2719,13 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI9" t="n">
         <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2752,7 +2752,7 @@
         <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2779,13 +2779,13 @@
         <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
         <v>30</v>
@@ -2836,7 +2836,7 @@
         <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>20</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
         <v>2.64</v>
       </c>
       <c r="K10" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L10" t="n">
         <v>1.63</v>
@@ -2919,22 +2919,22 @@
         <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
         <v>1.35</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
         <v>42</v>
@@ -2994,125 +2994,125 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="BN10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.35</v>
+        <v>2.54</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.1</v>
+        <v>2.82</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.08</v>
+        <v>1.83</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G11" t="n">
         <v>5.9</v>
@@ -3152,13 +3152,13 @@
         <v>1.95</v>
       </c>
       <c r="I11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.66</v>
@@ -3167,10 +3167,10 @@
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P11" t="n">
         <v>1.46</v>
@@ -3188,10 +3188,10 @@
         <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W11" t="n">
         <v>1.21</v>
@@ -3203,10 +3203,10 @@
         <v>6.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
         <v>13</v>
@@ -3260,13 +3260,13 @@
         <v>8.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
@@ -3275,34 +3275,34 @@
         <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="n">
         <v>2.64</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
         <v>8.800000000000001</v>
@@ -3362,11 +3362,11 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I12" t="n">
         <v>3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
@@ -3421,40 +3421,40 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
         <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T12" t="n">
         <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
         <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
         <v>23</v>
@@ -3466,7 +3466,7 @@
         <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>13.5</v>
@@ -3478,10 +3478,10 @@
         <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>34</v>
@@ -3493,16 +3493,16 @@
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
         <v>18.5</v>
@@ -3523,7 +3523,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
         <v>26</v>
@@ -3556,28 +3556,28 @@
         <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO12" t="n">
         <v>5.1</v>
@@ -3586,41 +3586,41 @@
         <v>17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BR12" t="n">
         <v>26</v>
       </c>
       <c r="BS12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
         <v>5.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX12" t="n">
         <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3651,46 +3651,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="I13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.46</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>1.6</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.58</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T13" t="n">
         <v>2.18</v>
@@ -3699,40 +3699,40 @@
         <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -3744,7 +3744,7 @@
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="AL13" t="n">
         <v>540</v>
@@ -3753,128 +3753,128 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AO13" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY13" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>15.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BD13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
         <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ13" t="n">
         <v>10</v>
       </c>
       <c r="BR13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BV13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3905,40 +3905,40 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H14" t="n">
         <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
@@ -3947,58 +3947,58 @@
         <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
         <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -4007,100 +4007,100 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX14" t="n">
         <v>12</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>12.5</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
         <v>2.92</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BT14" t="n">
         <v>6.6</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>12</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>14</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -4165,16 +4165,16 @@
         <v>3.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
         <v>2.54</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L15" t="n">
         <v>1.71</v>
@@ -4183,16 +4183,16 @@
         <v>1.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
         <v>1.71</v>
       </c>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.14</v>
@@ -4201,7 +4201,7 @@
         <v>7.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
@@ -4213,10 +4213,10 @@
         <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z15" t="n">
         <v>14</v>
@@ -4225,13 +4225,13 @@
         <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
         <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
         <v>44</v>
@@ -4240,25 +4240,25 @@
         <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
         <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AN15" t="n">
         <v>130</v>
@@ -4267,40 +4267,40 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
         <v>8.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
         <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>25</v>
       </c>
       <c r="BA15" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BB15" t="n">
         <v>75</v>
@@ -4312,10 +4312,10 @@
         <v>15</v>
       </c>
       <c r="BE15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BF15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG15" t="n">
         <v>44</v>
@@ -4345,7 +4345,7 @@
         <v>5.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BQ15" t="n">
         <v>9.4</v>
@@ -4354,7 +4354,7 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT15" t="n">
         <v>5.3</v>
@@ -4375,14 +4375,14 @@
         <v>10</v>
       </c>
       <c r="BZ15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
         <v>10</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -4416,67 +4416,67 @@
         <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q16" t="n">
         <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
         <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
         <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB16" t="n">
         <v>950</v>
@@ -4488,19 +4488,19 @@
         <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
         <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
         <v>23</v>
@@ -4518,40 +4518,40 @@
         <v>12.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
         <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA16" t="n">
         <v>36</v>
@@ -4563,52 +4563,52 @@
         <v>16.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>8.199999999999999</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L2" t="n">
         <v>3.7</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S2" t="n">
+        <v>26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X2" t="n">
         <v>4.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>470</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>13</v>
       </c>
-      <c r="AH2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH2" t="n">
-        <v>2.92</v>
+        <v>1.32</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>1.09</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>130</v>
+        <v>1.09</v>
       </c>
       <c r="BN2" t="n">
-        <v>5</v>
+        <v>800</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>1.09</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>1.09</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>1.09</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>10</v>
+        <v>1.09</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1111,82 +1111,82 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
         <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
         <v>2.62</v>
       </c>
       <c r="O3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.53</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.54</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R3" t="n">
         <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y3" t="n">
         <v>7.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>29</v>
@@ -1213,13 +1213,13 @@
         <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.4</v>
@@ -1228,113 +1228,113 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE3" t="n">
-        <v>9</v>
-      </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BT3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
@@ -1389,46 +1389,46 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="X4" t="n">
         <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
         <v>8.4</v>
@@ -1437,13 +1437,13 @@
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1455,19 +1455,19 @@
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK4" t="n">
         <v>50</v>
       </c>
-      <c r="AK4" t="n">
-        <v>65</v>
-      </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
@@ -1476,25 +1476,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
         <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
         <v>11.5</v>
@@ -1503,70 +1503,70 @@
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>8.4</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>8</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
@@ -1643,28 +1643,28 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
         <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1676,10 +1676,10 @@
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
         <v>90</v>
@@ -1691,10 +1691,10 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1706,34 +1706,34 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
         <v>23</v>
@@ -1748,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
         <v>15</v>
@@ -1763,22 +1763,22 @@
         <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1796,34 +1796,34 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU5" t="n">
         <v>4.9</v>
       </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW5" t="n">
         <v>10.5</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>15.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI6" t="n">
         <v>38</v>
       </c>
-      <c r="AF6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>42</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
         <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>8.4</v>
       </c>
       <c r="AV6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX6" t="n">
         <v>14</v>
       </c>
-      <c r="AW6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
         <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM6" t="n">
         <v>12.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>23</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
         <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA6" t="n">
         <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2127,67 +2127,67 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
         <v>2.52</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T7" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>310</v>
       </c>
       <c r="AA7" t="n">
         <v>46</v>
@@ -2196,55 +2196,55 @@
         <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
         <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
@@ -2253,79 +2253,79 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
         <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BE7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
         <v>5.4</v>
@@ -2334,23 +2334,23 @@
         <v>22</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX7" t="n">
         <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I8" t="n">
         <v>2.68</v>
@@ -2408,34 +2408,34 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
         <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W8" t="n">
         <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
         <v>14.5</v>
@@ -2444,13 +2444,13 @@
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>12.5</v>
@@ -2480,13 +2480,13 @@
         <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
@@ -2498,13 +2498,13 @@
         <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2519,10 +2519,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BB8" t="n">
         <v>34</v>
@@ -2531,7 +2531,7 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
@@ -2540,71 +2540,71 @@
         <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>90</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP8" t="n">
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>30</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
         <v>3.6</v>
@@ -2665,25 +2665,25 @@
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
         <v>1.58</v>
@@ -2692,10 +2692,10 @@
         <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
         <v>42</v>
@@ -2707,43 +2707,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL9" t="n">
         <v>36</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>34</v>
-      </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2752,13 +2752,13 @@
         <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2767,70 +2767,70 @@
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
         <v>16</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL9" t="n">
         <v>90</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>6.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
         <v>6.4</v>
@@ -2848,17 +2848,17 @@
         <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
         <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K10" t="n">
         <v>2.94</v>
@@ -2913,13 +2913,13 @@
         <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q10" t="n">
         <v>2.8</v>
@@ -2928,22 +2928,22 @@
         <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2979,7 +2979,7 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2994,125 +2994,125 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT10" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="AX10" t="n">
-        <v>6</v>
+        <v>1.79</v>
       </c>
       <c r="AY10" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.04</v>
+        <v>5.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.2</v>
+        <v>1.69</v>
       </c>
       <c r="BC10" t="n">
         <v>3.95</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.15</v>
+        <v>1.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>1.35</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.86</v>
+        <v>1.35</v>
       </c>
       <c r="BN10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>1.35</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2.54</v>
+        <v>1.35</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.82</v>
+        <v>1.35</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3143,79 +3143,79 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="L11" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.15</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13</v>
-      </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
         <v>65</v>
@@ -3224,10 +3224,10 @@
         <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AH11" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3245,128 +3245,128 @@
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
         <v>8.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BO11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -3421,7 +3421,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
@@ -3439,19 +3439,19 @@
         <v>2.76</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
         <v>1.65</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
         <v>16</v>
@@ -3460,7 +3460,7 @@
         <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB12" t="n">
         <v>14</v>
@@ -3469,7 +3469,7 @@
         <v>8.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>29</v>
@@ -3481,16 +3481,16 @@
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI12" t="n">
         <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>29</v>
@@ -3505,7 +3505,7 @@
         <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
@@ -3514,7 +3514,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
@@ -3538,25 +3538,25 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD12" t="n">
         <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4</v>
@@ -3604,7 +3604,7 @@
         <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BX12" t="n">
         <v>28</v>
@@ -3616,11 +3616,11 @@
         <v>18.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3654,37 +3654,37 @@
         <v>3.45</v>
       </c>
       <c r="G13" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
@@ -3693,13 +3693,13 @@
         <v>5.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
         <v>1.3</v>
@@ -3711,10 +3711,10 @@
         <v>7.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
         <v>9.800000000000001</v>
@@ -3723,46 +3723,46 @@
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="AL13" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AO13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP13" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
         <v>12.5</v>
@@ -3771,7 +3771,7 @@
         <v>18.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
@@ -3792,25 +3792,25 @@
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
       </c>
       <c r="BD13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>9.6</v>
       </c>
       <c r="BH13" t="n">
         <v>2.62</v>
@@ -3852,7 +3852,7 @@
         <v>5.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>24</v>
@@ -3861,7 +3861,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
         <v>10.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
@@ -3923,46 +3923,46 @@
         <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
         <v>23</v>
@@ -3971,34 +3971,34 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AF14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -4007,82 +4007,82 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AT14" t="n">
         <v>7.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AX14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>12</v>
       </c>
-      <c r="AY14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH14" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BN14" t="n">
         <v>5.2</v>
@@ -4094,16 +4094,16 @@
         <v>21</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
         <v>5.8</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H15" t="n">
         <v>2.48</v>
@@ -4180,16 +4180,16 @@
         <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N15" t="n">
         <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
         <v>3.2</v>
@@ -4201,7 +4201,7 @@
         <v>7.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
@@ -4210,16 +4210,16 @@
         <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
         <v>42</v>
@@ -4231,16 +4231,16 @@
         <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH15" t="n">
         <v>30</v>
@@ -4261,7 +4261,7 @@
         <v>290</v>
       </c>
       <c r="AN15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4276,13 +4276,13 @@
         <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AT15" t="n">
         <v>8.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
         <v>12</v>
@@ -4291,7 +4291,7 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY15" t="n">
         <v>16.5</v>
@@ -4300,7 +4300,7 @@
         <v>25</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.5</v>
+        <v>70</v>
       </c>
       <c r="BB15" t="n">
         <v>75</v>
@@ -4309,52 +4309,52 @@
         <v>60</v>
       </c>
       <c r="BD15" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="BE15" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG15" t="n">
         <v>44</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
         <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP15" t="n">
         <v>42</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT15" t="n">
         <v>5.3</v>
@@ -4366,13 +4366,13 @@
         <v>26</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
         <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4440,37 +4440,37 @@
         <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
         <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
         <v>32</v>
@@ -4497,7 +4497,7 @@
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>50</v>
@@ -4509,19 +4509,19 @@
         <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM16" t="n">
         <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
         <v>16</v>
@@ -4533,31 +4533,31 @@
         <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
         <v>16.5</v>
@@ -4566,7 +4566,7 @@
         <v>26</v>
       </c>
       <c r="BE16" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
@@ -4575,68 +4575,68 @@
         <v>32</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU16" t="n">
         <v>5.7</v>
       </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,114 +843,114 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Livyi Bereh</t>
+          <t>Agrobiznes Volochysk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>FK Kudrivka</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6</v>
+        <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>2.82</v>
+        <v>48</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="R2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.03</v>
       </c>
-      <c r="S2" t="n">
-        <v>26</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
         <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -959,135 +959,135 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>1.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.9</v>
+        <v>2.82</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>1.11</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.7</v>
+        <v>2.82</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>1.11</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.6</v>
+        <v>2.82</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>1.11</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>2.48</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.32</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Agrobiznes Volochysk</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Kudrivka</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H3" t="n">
         <v>4.1</v>
       </c>
-      <c r="G3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.26</v>
-      </c>
       <c r="I3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.68</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB3" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>440</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT3" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="BK3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
         <v>9</v>
       </c>
-      <c r="AU3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.42</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI4" t="n">
         <v>3.4</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BJ4" t="n">
         <v>9</v>
       </c>
-      <c r="AR4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11</v>
-      </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X5" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI5" t="n">
         <v>3.8</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="BJ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM5" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7.6</v>
       </c>
       <c r="BN5" t="n">
         <v>5.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
         <v>4.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -1864,151 +1864,151 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="I6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.7</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
         <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AI6" t="n">
         <v>36</v>
       </c>
-      <c r="AF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS6" t="n">
         <v>38</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>50</v>
       </c>
       <c r="AT6" t="n">
         <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
@@ -2017,70 +2017,70 @@
         <v>32</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BM6" t="n">
         <v>12.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
@@ -2089,14 +2089,14 @@
         <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.34</v>
@@ -2151,91 +2151,91 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
         <v>34</v>
       </c>
-      <c r="AK7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>32</v>
-      </c>
       <c r="AM7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>14</v>
@@ -2244,113 +2244,113 @@
         <v>19</v>
       </c>
       <c r="AS7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>25</v>
       </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>26</v>
-      </c>
       <c r="AX7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB7" t="n">
         <v>32</v>
       </c>
-      <c r="BB7" t="n">
-        <v>30</v>
-      </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>90</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BR7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="I8" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2399,7 +2399,7 @@
         <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2411,16 +2411,16 @@
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
@@ -2429,189 +2429,189 @@
         <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
         <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
         <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
         <v>34</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG8" t="n">
         <v>17</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>15</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>30</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,244 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.54</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>2.82</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
         <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>14.5</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.5</v>
+        <v>2.54</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV9" t="n">
         <v>12</v>
       </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>2.56</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>2.34</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>2.52</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>5.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>2.56</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>2.56</v>
       </c>
       <c r="BE9" t="n">
-        <v>42</v>
+        <v>2.6</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>16</v>
+        <v>2.44</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -2880,97 +2880,97 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>4.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="J10" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L10" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.15</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="S10" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.69</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
@@ -2979,147 +2979,147 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>270</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.89</v>
+        <v>9.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.71</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.79</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.69</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.71</v>
+        <v>9.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.72</v>
+        <v>9.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.92</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.71</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.35</v>
+        <v>32</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.35</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.3</v>
       </c>
-      <c r="I11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>6.6</v>
+        <v>2.82</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>14</v>
       </c>
-      <c r="AA11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AR11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="BL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV11" t="n">
         <v>21</v>
       </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="BW11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.5</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>2.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>2.76</v>
+        <v>5.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS12" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BB12" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>29</v>
       </c>
       <c r="BC12" t="n">
         <v>23</v>
       </c>
       <c r="BD12" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
         <v>13</v>
       </c>
-      <c r="BG12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BN12" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BO12" t="n">
         <v>5.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY12" t="n">
         <v>11</v>
       </c>
-      <c r="BT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BZ12" t="n">
-        <v>18.5</v>
+        <v>60</v>
       </c>
       <c r="CA12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,189 +3637,189 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
-        <v>3.85</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>2.66</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AR13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF13" t="n">
         <v>24</v>
       </c>
-      <c r="AG13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>12</v>
       </c>
       <c r="BK13" t="n">
         <v>6.4</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="CA13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW14" t="n">
         <v>21</v>
       </c>
-      <c r="AI14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AX14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE14" t="n">
         <v>38</v>
       </c>
-      <c r="AK14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="BF14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>9</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY14" t="n">
         <v>9.6</v>
       </c>
-      <c r="AR14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="CA14" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,498 +4145,244 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
         <v>3.85</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.48</v>
-      </c>
       <c r="I15" t="n">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI15" t="n">
         <v>3.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="BJ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
         <v>7</v>
       </c>
-      <c r="Y15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="BT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>75</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>90</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>10</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Atletico Ottawa</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>FC Supra du Quebec</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,768 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Nautico PE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fortaleza EC</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S2" t="n">
-        <v>34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>390</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-09 20:43:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Cuiaba</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-09 20:43:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Atletico Ottawa</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FC Supra du Quebec</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>950</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>860</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
